--- a/test/excel/paste/painter/onto-merged-painter.xlsx
+++ b/test/excel/paste/painter/onto-merged-painter.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fsave-48173/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fsave-50444/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{686A1028-CC97-9841-A045-E2D958C20979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C99E7235-4302-C54A-A03B-B6798B980C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -547,7 +547,6 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
         <v>7</v>
       </c>
@@ -562,7 +561,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I14">
+  <conditionalFormatting sqref="H14:I14">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
